--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K122"/>
+  <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1395,38 +1395,6 @@
       <c r="A26" t="n">
         <v>1</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>1714</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-1714</v>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2064,38 +2032,6 @@
       <c r="A46" t="n">
         <v>2</v>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Bungkil Kedelai</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>7984</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>1198</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-1198</v>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2138,38 +2074,6 @@
       <c r="A48" t="n">
         <v>4</v>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>404</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-404</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -2546,89 +2450,57 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>4039</v>
+        <v>2830</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>606</v>
+        <v>0</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>263</v>
+        <v>354</v>
       </c>
       <c r="H61" t="n">
-        <v>-343</v>
+        <v>354</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>5</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>354</v>
-      </c>
-      <c r="H62" t="n">
-        <v>354</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Biji Kapuk</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4168</v>
+        <v>3332</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2644,10 +2516,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="H63" t="n">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2657,60 +2529,60 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>3332</v>
+        <v>7984</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>400</v>
+        <v>-958</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7984</v>
+        <v>8637</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>958</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2721,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-958</v>
+        <v>-864</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2731,23 +2603,23 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Bungkil Sawit</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8637</v>
+        <v>8201</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>656</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2758,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-864</v>
+        <v>-656</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2768,15 +2640,15 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8201</v>
+        <v>3202</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2784,36 +2656,36 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>656</v>
+        <v>256</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>176</v>
       </c>
       <c r="H67" t="n">
-        <v>-656</v>
+        <v>-80</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3202</v>
+        <v>4764</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2821,129 +2693,129 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-80</v>
+        <v>-381</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pollard</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>4764</v>
+        <v>8149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>381</v>
+        <v>0</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
       <c r="H69" t="n">
-        <v>-381</v>
+        <v>448</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8149</v>
+        <v>3637</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>1.1%</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>448</v>
+        <v>40</v>
       </c>
       <c r="H70" t="n">
-        <v>448</v>
+        <v>-142</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>3637</v>
+        <v>4006</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="H71" t="n">
-        <v>-142</v>
+        <v>-96</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -2953,137 +2825,137 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4006</v>
+        <v>7908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-96</v>
+        <v>-119</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
-        <v>16</v>
-      </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>7908</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>119</v>
+        <v>5590</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>3493</v>
       </c>
       <c r="H73" t="n">
-        <v>-119</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>2097</v>
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>5590</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G74" t="n">
-        <v>3493</v>
-      </c>
-      <c r="H74" t="n">
-        <v>2097</v>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Rp5,590/kg -&gt; Rp3,493/kg | HEMAT Rp2,097/kg (37.5%)</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Rp5,590/kg -&gt; Rp3,493/kg | HEMAT Rp2,097/kg (37.5%)</t>
+          <t>Sapi Perah Produksi Tinggi</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sapi Perah Produksi Tinggi</t>
+      <c r="A76" t="n">
+        <v>2</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Bungkil Kedelai</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>7984</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>18%</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1437</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-1437</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>7984</v>
+        <v>8059</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1437</v>
+        <v>645</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -3094,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1437</v>
+        <v>-645</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3104,15 +2976,15 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bungkil Kacang Tanah</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8059</v>
+        <v>8637</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3120,7 +2992,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>645</v>
+        <v>691</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -3131,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-645</v>
+        <v>-691</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3141,15 +3013,15 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8637</v>
+        <v>4039</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3157,7 +3029,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>691</v>
+        <v>323</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -3168,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-691</v>
+        <v>-323</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3178,23 +3050,23 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>323</v>
+        <v>192</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -3205,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-323</v>
+        <v>-192</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3215,52 +3087,20 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Gaplek</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>3202</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>192</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-192</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>7515</v>
+        <v>8023</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3268,7 +3108,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -3279,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-376</v>
+        <v>-401</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3289,60 +3129,28 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Tepung Ikan</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>8023</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>401</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-401</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>3637</v>
+        <v>7908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -3353,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-182</v>
+        <v>-158</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3362,101 +3170,101 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
-        <v>10</v>
-      </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>7908</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>158</v>
+        <v>6119</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>-158</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>6119</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Sapi Hamil 7-9 Bulan</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sapi Hamil 7-9 Bulan</t>
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-1371</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4896</v>
+        <v>4039</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1371</v>
+        <v>727</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3467,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-1371</v>
+        <v>-727</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -3477,23 +3285,23 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>727</v>
+        <v>320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3504,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-727</v>
+        <v>-320</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -3514,15 +3322,15 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>3202</v>
+        <v>7984</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3530,7 +3338,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>320</v>
+        <v>798</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3541,7 +3349,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-320</v>
+        <v>-798</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -3551,15 +3359,15 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7984</v>
+        <v>4764</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3567,7 +3375,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>798</v>
+        <v>476</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3578,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-798</v>
+        <v>-476</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -3588,23 +3396,23 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pollard</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4764</v>
+        <v>2386</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>476</v>
+        <v>119</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3615,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-476</v>
+        <v>-119</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -3625,15 +3433,15 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>2386</v>
+        <v>3637</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3641,7 +3449,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3652,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-119</v>
+        <v>-182</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -3662,23 +3470,23 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3637</v>
+        <v>4006</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3689,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-182</v>
+        <v>-100</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -3699,277 +3507,245 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>9</v>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E96" t="n">
-        <v>100</v>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>10</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>10</v>
-      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>7908</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>119</v>
+        <v>5033</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-119</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>5033</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Sapi Laktasi Ringan</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sapi Laktasi Ringan</t>
+      <c r="A100" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1567</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>211</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-1356</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4896</v>
+        <v>2830</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1567</v>
+        <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>211</v>
+        <v>405</v>
       </c>
       <c r="H101" t="n">
-        <v>-1356</v>
+        <v>405</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>2830</v>
+        <v>7984</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>1118</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>405</v>
+        <v>-1118</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7984</v>
+        <v>4039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1118</v>
+        <v>485</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="H103" t="n">
-        <v>-1118</v>
+        <v>-336</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4039</v>
+        <v>4933</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>149</v>
+        <v>562</v>
       </c>
       <c r="H104" t="n">
-        <v>-336</v>
+        <v>562</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>4933</v>
+        <v>3582</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3981,14 +3757,14 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>562</v>
+        <v>383</v>
       </c>
       <c r="H105" t="n">
-        <v>562</v>
+        <v>383</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -3998,15 +3774,15 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>3582</v>
+        <v>2386</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -4018,14 +3794,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>383</v>
+        <v>222</v>
       </c>
       <c r="H106" t="n">
-        <v>383</v>
+        <v>222</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -4035,52 +3811,52 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>2386</v>
+        <v>3202</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>222</v>
+        <v>192</v>
       </c>
       <c r="H107" t="n">
-        <v>222</v>
+        <v>-64</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>3202</v>
+        <v>8059</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -4088,18 +3864,18 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>256</v>
+        <v>645</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="H108" t="n">
-        <v>-64</v>
+        <v>-419</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
@@ -4109,15 +3885,15 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bungkil Kacang Tanah</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8059</v>
+        <v>8637</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -4125,36 +3901,36 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>645</v>
+        <v>691</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>226</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>-419</v>
+        <v>-691</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8637</v>
+        <v>4764</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -4162,147 +3938,83 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>691</v>
+        <v>381</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H110" t="n">
-        <v>-691</v>
+        <v>-357</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>11</v>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E111" t="n">
-        <v>381</v>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G111" t="n">
-        <v>24</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>3637</v>
+        <v>8023</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>262</v>
+        <v>481</v>
       </c>
       <c r="H112" t="n">
-        <v>80</v>
+        <v>481</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>13</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Tepung Ikan</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>8023</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>0</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>481</v>
-      </c>
-      <c r="H113" t="n">
-        <v>481</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Biji Kapuk</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>4168</v>
+        <v>3332</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4314,14 +4026,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="H114" t="n">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -4331,15 +4043,15 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3332</v>
+        <v>5211</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4351,14 +4063,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="H115" t="n">
-        <v>197</v>
+        <v>245</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -4368,217 +4080,180 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
+        <v>17</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Dedak Halus</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>140</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>156</v>
+      </c>
+      <c r="H116" t="n">
         <v>16</v>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Menir</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>5211</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>245</v>
-      </c>
-      <c r="H116" t="n">
-        <v>245</v>
-      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>OK</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>4006</v>
+        <v>8149</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="H117" t="n">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>8149</v>
+        <v>7908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>171</v>
+        <v>-119</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>7908</v>
+        <v>5148</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="H119" t="n">
-        <v>-119</v>
+        <v>62</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>20</v>
-      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>5148</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>5583</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>62</v>
+        <v>4195</v>
       </c>
       <c r="H120" t="n">
-        <v>62</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1388</v>
       </c>
     </row>
     <row r="121">
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E121" t="n">
-        <v>5583</v>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G121" t="n">
-        <v>4195</v>
-      </c>
-      <c r="H121" t="n">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
+      <c r="A121" t="inlineStr">
         <is>
           <t>Rp5,583/kg -&gt; Rp4,195/kg | HEMAT Rp1,388/kg (24.9%)</t>
         </is>
@@ -4614,7 +4289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -5298,38 +4973,6 @@
       <c r="A24" t="n">
         <v>1</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>1469</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>6.9%</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>338</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-1131</v>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -6150,23 +5793,23 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4896</v>
+        <v>7984</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1469</v>
+        <v>1198</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6177,7 +5820,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1469</v>
+        <v>-1198</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -6187,60 +5830,28 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Bungkil Kedelai</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>7984</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>1198</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-1198</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>485</v>
+        <v>256</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6251,7 +5862,7 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>-485</v>
+        <v>-256</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -6261,15 +5872,15 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3202</v>
+        <v>8059</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6277,7 +5888,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>256</v>
+        <v>645</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6288,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>-256</v>
+        <v>-645</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -6298,15 +5909,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bungkil Kacang Tanah</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8059</v>
+        <v>8637</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6314,7 +5925,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>645</v>
+        <v>691</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6325,7 +5936,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-645</v>
+        <v>-691</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -6335,23 +5946,23 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8637</v>
+        <v>4006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>691</v>
+        <v>240</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6362,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-691</v>
+        <v>-240</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -6372,23 +5983,23 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>4006</v>
+        <v>3637</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>240</v>
+        <v>182</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6399,7 +6010,7 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-240</v>
+        <v>-182</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -6409,23 +6020,23 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3637</v>
+        <v>7515</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>182</v>
+        <v>263</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6436,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-182</v>
+        <v>-263</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -6446,23 +6057,23 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>7515</v>
+        <v>8023</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6473,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-263</v>
+        <v>-241</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -6483,23 +6094,23 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8023</v>
+        <v>7908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>241</v>
+        <v>119</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6510,7 +6121,7 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-241</v>
+        <v>-119</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -6519,101 +6130,101 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
-        <v>11</v>
-      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>7908</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>119</v>
+        <v>5787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-119</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>5787</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Rp5,787/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Rp5,787/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Domba Konservasi</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Domba Konservasi</t>
+      <c r="A62" t="n">
+        <v>3</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Dedak Padi</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>4039</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>889</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>-889</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Jagung Pipilan</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>4039</v>
+        <v>4896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>889</v>
+        <v>979</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6624,7 +6235,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-889</v>
+        <v>-979</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -6634,174 +6245,153 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>5</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>979</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-979</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Biji Kapuk</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3202</v>
+        <v>4168</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>227</v>
+        <v>329</v>
       </c>
       <c r="H65" t="n">
-        <v>-157</v>
+        <v>329</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
-        <v>10</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Biji Kapuk</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>4168</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>329</v>
-      </c>
-      <c r="H66" t="n">
-        <v>329</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>BARU</t>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Rp4,307/kg -&gt; Rp3,077/kg | HEMAT Rp1,230/kg (28.6%)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>4307</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>3077</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1230</v>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Domba Pedaging</t>
+        </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Rp4,307/kg -&gt; Rp3,077/kg | HEMAT Rp1,230/kg (28.6%)</t>
+      <c r="A68" t="n">
+        <v>1</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-1371</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Domba Pedaging</t>
+      <c r="A69" t="n">
+        <v>2</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dedak Padi</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>4039</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>15%</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>606</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-606</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Sawit</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4896</v>
+        <v>8201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1371</v>
+        <v>820</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -6812,7 +6402,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-1371</v>
+        <v>-820</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -6822,23 +6412,23 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>606</v>
+        <v>320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -6849,7 +6439,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-606</v>
+        <v>-320</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -6859,23 +6449,23 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8201</v>
+        <v>4006</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>820</v>
+        <v>320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -6886,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-820</v>
+        <v>-320</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -6896,23 +6486,23 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3202</v>
+        <v>4764</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>320</v>
+        <v>381</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -6923,7 +6513,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-320</v>
+        <v>-381</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -6933,23 +6523,23 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>4006</v>
+        <v>5148</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>320</v>
+        <v>154</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6960,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-320</v>
+        <v>-154</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -6970,23 +6560,23 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pollard</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4764</v>
+        <v>7908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>381</v>
+        <v>79</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6997,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-381</v>
+        <v>-79</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -7006,107 +6596,33 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
-        <v>9</v>
-      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>5148</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>154</v>
+        <v>5192</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-154</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
-        <v>10</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
-      </c>
-      <c r="E77" t="n">
-        <v>79</v>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-79</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>5192</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>Rp5,192/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
@@ -7138,7 +6654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -7859,38 +7375,6 @@
       <c r="A25" t="n">
         <v>1</v>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>1860</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-1860</v>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -8528,38 +8012,6 @@
       <c r="A45" t="n">
         <v>2</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Menir</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>5211</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>782</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-782</v>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -8602,38 +8054,6 @@
       <c r="A47" t="n">
         <v>4</v>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Corn Gluten Feed</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>7515</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>601</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-601</v>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -9012,38 +8432,6 @@
       <c r="A60" t="n">
         <v>5</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>17.4%</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>492</v>
-      </c>
-      <c r="H60" t="n">
-        <v>492</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9086,38 +8474,6 @@
       <c r="A62" t="n">
         <v>7</v>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>485</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-485</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9752,33 +9108,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>6039</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>Rp6,039/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
@@ -9810,7 +9140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K150"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10346,38 +9676,6 @@
       <c r="A20" t="n">
         <v>1</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>1860</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>13.9%</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>681</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-1179</v>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11087,126 +10385,94 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4896</v>
+        <v>7984</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>42%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2056</v>
+        <v>1437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>602</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-1454</v>
+        <v>-1437</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Bungkil Kedelai</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>7984</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>1437</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-1437</v>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5211</v>
+        <v>3202</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>672</v>
+        <v>416</v>
       </c>
       <c r="H44" t="n">
-        <v>-58</v>
+        <v>416</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3202</v>
+        <v>2386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -11218,14 +10484,14 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>416</v>
+        <v>272</v>
       </c>
       <c r="H45" t="n">
-        <v>416</v>
+        <v>272</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -11235,15 +10501,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>2386</v>
+        <v>5148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -11255,14 +10521,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>272</v>
+        <v>458</v>
       </c>
       <c r="H46" t="n">
-        <v>272</v>
+        <v>458</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -11272,15 +10538,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sorgum</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5148</v>
+        <v>2830</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -11292,14 +10558,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>458</v>
+        <v>221</v>
       </c>
       <c r="H47" t="n">
-        <v>458</v>
+        <v>221</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -11309,108 +10575,108 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>2830</v>
+        <v>7515</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>451</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>221</v>
+        <v>-451</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>7515</v>
+        <v>8149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>451</v>
+        <v>244</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="H49" t="n">
-        <v>-451</v>
+        <v>172</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8149</v>
+        <v>8023</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>244</v>
+        <v>401</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>416</v>
+        <v>321</v>
       </c>
       <c r="H50" t="n">
-        <v>172</v>
+        <v>-80</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -11420,34 +10686,34 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8023</v>
+        <v>3637</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>401</v>
+        <v>73</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>321</v>
+        <v>182</v>
       </c>
       <c r="H51" t="n">
-        <v>-80</v>
+        <v>109</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -11457,97 +10723,97 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Tepung Bulu Ayam</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3637</v>
+        <v>8038</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>182</v>
+        <v>354</v>
       </c>
       <c r="H52" t="n">
-        <v>109</v>
+        <v>354</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tepung Bulu Ayam</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8038</v>
+        <v>4039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>354</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>354</v>
+        <v>-162</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -11558,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-162</v>
+        <v>-107</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -11568,89 +10834,89 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>3582</v>
+        <v>8059</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="H55" t="n">
-        <v>-107</v>
+        <v>193</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Bungkil Kacang Tanah</t>
+          <t>Bungkil Sawit</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8059</v>
+        <v>8201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>193</v>
+        <v>-123</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8201</v>
+        <v>7908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -11658,7 +10924,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -11669,7 +10935,7 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-123</v>
+        <v>-119</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -11679,52 +10945,52 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>7908</v>
+        <v>8637</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H58" t="n">
-        <v>-119</v>
+        <v>43</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8637</v>
+        <v>3332</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -11736,14 +11002,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="H59" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -11752,101 +11018,101 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
-        <v>20</v>
-      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>3332</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>5903</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>10</v>
+        <v>4661</v>
       </c>
       <c r="H60" t="n">
-        <v>10</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1242</v>
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>5903</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>4661</v>
-      </c>
-      <c r="H61" t="n">
-        <v>1242</v>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Rp5,903/kg -&gt; Rp4,661/kg | HEMAT Rp1,242/kg (21.0%)</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Rp5,903/kg -&gt; Rp4,661/kg | HEMAT Rp1,242/kg (21.0%)</t>
+          <t>Layer Grower (7-17wk)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Layer Grower (7-17wk)</t>
+      <c r="A63" t="n">
+        <v>1</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-1860</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>4896</v>
+        <v>5211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1860</v>
+        <v>625</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -11857,7 +11123,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-1860</v>
+        <v>-625</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -11867,23 +11133,23 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>5211</v>
+        <v>7515</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>625</v>
+        <v>451</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -11894,7 +11160,7 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-625</v>
+        <v>-451</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -11904,60 +11170,28 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Corn Gluten Feed</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>7515</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>451</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-451</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -11968,7 +11202,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-202</v>
+        <v>-143</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -11978,60 +11212,28 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>6</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>143</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-143</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8023</v>
+        <v>8149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -12042,7 +11244,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-321</v>
+        <v>-244</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -12052,15 +11254,15 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Bungkil Sawit</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8149</v>
+        <v>8201</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -12068,7 +11270,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -12079,7 +11281,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-244</v>
+        <v>-246</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -12089,23 +11291,23 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8201</v>
+        <v>4006</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>246</v>
+        <v>100</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -12116,7 +11318,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-246</v>
+        <v>-100</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -12126,15 +11328,15 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4006</v>
+        <v>7908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -12142,7 +11344,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100</v>
+        <v>198</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -12153,7 +11355,7 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-100</v>
+        <v>-198</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -12163,23 +11365,23 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7908</v>
+        <v>3637</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -12190,7 +11392,7 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-198</v>
+        <v>-73</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -12199,101 +11401,101 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
-        <v>12</v>
-      </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Molases</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>3637</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>73</v>
+        <v>5901</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-73</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E75" t="n">
-        <v>5901</v>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0</v>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Rp5,901/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Rp5,901/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Layer Pre-Lay (17-18wk)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Layer Pre-Lay (17-18wk)</t>
+      <c r="A77" t="n">
+        <v>2</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bungkil Kedelai</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>7984</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>17%</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-1357</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7984</v>
+        <v>7908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1357</v>
+        <v>633</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -12304,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1357</v>
+        <v>-633</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -12314,23 +11516,23 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>7908</v>
+        <v>7515</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>633</v>
+        <v>376</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -12341,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-633</v>
+        <v>-376</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -12351,15 +11553,15 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>7515</v>
+        <v>4039</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -12367,7 +11569,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>376</v>
+        <v>202</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -12378,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-376</v>
+        <v>-202</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -12388,23 +11590,23 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -12415,7 +11617,7 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-202</v>
+        <v>-143</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -12425,15 +11627,15 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>3582</v>
+        <v>4006</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -12441,7 +11643,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -12452,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>-143</v>
+        <v>-160</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -12462,60 +11664,28 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>8</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>160</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-160</v>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8023</v>
+        <v>8149</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>321</v>
+        <v>244</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -12526,7 +11696,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-321</v>
+        <v>-244</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -12536,137 +11706,105 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>10</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>244</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-244</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
-        <v>11</v>
-      </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>8201</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>246</v>
+        <v>5990</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G86" t="n">
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>-246</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>5990</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0</v>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Rp5,990/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Rp5,990/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Layer Produksi</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Layer Produksi</t>
+      <c r="A89" t="n">
+        <v>1</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-1616</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4896</v>
+        <v>7984</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1616</v>
+        <v>1277</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -12677,7 +11815,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-1616</v>
+        <v>-1277</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -12687,23 +11825,23 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7984</v>
+        <v>7908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1277</v>
+        <v>1186</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -12714,7 +11852,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-1277</v>
+        <v>-1186</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -12724,23 +11862,23 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>7908</v>
+        <v>5211</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1186</v>
+        <v>521</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -12751,7 +11889,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-1186</v>
+        <v>-521</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -12761,23 +11899,23 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>5211</v>
+        <v>8149</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>521</v>
+        <v>244</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -12788,7 +11926,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-521</v>
+        <v>-244</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -12798,15 +11936,15 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>8149</v>
+        <v>3582</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12814,7 +11952,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>244</v>
+        <v>107</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -12825,7 +11963,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-244</v>
+        <v>-107</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -12835,15 +11973,15 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3582</v>
+        <v>8023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12851,7 +11989,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12862,7 +12000,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-107</v>
+        <v>-241</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -12872,23 +12010,23 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>8023</v>
+        <v>4006</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -12899,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-241</v>
+        <v>-80</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -12908,93 +12046,61 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
-        <v>11</v>
-      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>4006</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>80</v>
+        <v>6170</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G97" t="n">
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>-80</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E98" t="n">
-        <v>6170</v>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G98" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0</v>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Rp6,170/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Rp6,170/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Bebek Petelur Starter</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Bebek Petelur Starter</t>
-        </is>
+      <c r="A100" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2386</v>
+        <v>2830</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13006,14 +12112,14 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="H101" t="n">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -13023,89 +12129,57 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>3</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>22.4%</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>634</v>
-      </c>
-      <c r="H102" t="n">
-        <v>634</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>7984</v>
+        <v>3202</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1597</v>
+        <v>0</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>493</v>
       </c>
       <c r="H103" t="n">
-        <v>-1597</v>
+        <v>493</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3202</v>
+        <v>3332</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13117,14 +12191,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="H104" t="n">
-        <v>493</v>
+        <v>423</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
@@ -13134,200 +12208,200 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3332</v>
+        <v>5211</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>625</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>423</v>
+        <v>-625</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Biji Kapuk</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>5211</v>
+        <v>4168</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="H106" t="n">
-        <v>-625</v>
+        <v>358</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Biji Kapuk</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>4168</v>
+        <v>8149</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>358</v>
+        <v>603</v>
       </c>
       <c r="H107" t="n">
-        <v>358</v>
+        <v>277</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Tepung Bulu Ayam</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8149</v>
+        <v>8038</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>326</v>
+        <v>0</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>603</v>
+        <v>506</v>
       </c>
       <c r="H108" t="n">
-        <v>277</v>
+        <v>506</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Tepung Bulu Ayam</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>8038</v>
+        <v>4006</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="H109" t="n">
-        <v>506</v>
+        <v>-240</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>4006</v>
+        <v>8023</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13335,7 +12409,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>240</v>
+        <v>481</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13346,7 +12420,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-240</v>
+        <v>-481</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -13356,23 +12430,23 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8023</v>
+        <v>7515</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>481</v>
+        <v>376</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13383,7 +12457,7 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>-481</v>
+        <v>-376</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
@@ -13393,15 +12467,15 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>7515</v>
+        <v>4039</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13409,7 +12483,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>376</v>
+        <v>202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13420,7 +12494,7 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>-376</v>
+        <v>-202</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -13430,71 +12504,71 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H113" t="n">
-        <v>-202</v>
+        <v>-53</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3582</v>
+        <v>7908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="H114" t="n">
-        <v>-53</v>
+        <v>-79</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -13504,15 +12578,15 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>7908</v>
+        <v>3637</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13520,121 +12594,121 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>158</v>
+        <v>73</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-79</v>
+        <v>-73</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>17</v>
-      </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Molases</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>3637</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>73</v>
+        <v>5899</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>3739</v>
       </c>
       <c r="H116" t="n">
-        <v>-73</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>2160</v>
       </c>
     </row>
     <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>5899</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>3739</v>
-      </c>
-      <c r="H117" t="n">
-        <v>2160</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
+        </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
+          <t>Bebek Petelur Layer</t>
         </is>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Bebek Petelur Layer</t>
+      <c r="A119" t="n">
+        <v>5</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Dedak Padi</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4039</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>242</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-242</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>7908</v>
+        <v>4006</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>949</v>
+        <v>160</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13645,7 +12719,7 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>-949</v>
+        <v>-160</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
@@ -13655,23 +12729,23 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>242</v>
+        <v>107</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13682,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-242</v>
+        <v>-107</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -13692,23 +12766,23 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Bungkil Sawit</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4006</v>
+        <v>8201</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>160</v>
+        <v>246</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13719,7 +12793,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>-160</v>
+        <v>-246</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -13729,15 +12803,15 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3582</v>
+        <v>8023</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13745,7 +12819,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13756,7 +12830,7 @@
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>-107</v>
+        <v>-241</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -13765,149 +12839,149 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>10</v>
-      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>8201</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>246</v>
+        <v>6053</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>-246</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>11</v>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Tepung Ikan</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>8023</v>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>241</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>0</v>
-      </c>
-      <c r="H125" t="n">
-        <v>-241</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>6053</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>0</v>
-      </c>
-      <c r="H126" t="n">
-        <v>0</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Bebek Pedaging (Peking)</t>
+        </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+      <c r="A127" t="n">
+        <v>1</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>1860</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>8.0%</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>392</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-1468</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Bebek Pedaging (Peking)</t>
+      <c r="A128" t="n">
+        <v>2</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Onggok</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2386</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>18.5%</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>441</v>
+      </c>
+      <c r="H128" t="n">
+        <v>441</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>4896</v>
+        <v>7984</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1860</v>
+        <v>1437</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>392</v>
+        <v>232</v>
       </c>
       <c r="H129" t="n">
-        <v>-1468</v>
+        <v>-1205</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -13917,15 +12991,15 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>2386</v>
+        <v>3202</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13937,14 +13011,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>441</v>
+        <v>519</v>
       </c>
       <c r="H130" t="n">
-        <v>441</v>
+        <v>519</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
@@ -13954,34 +13028,34 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>7984</v>
+        <v>5211</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1437</v>
+        <v>625</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>232</v>
+        <v>500</v>
       </c>
       <c r="H131" t="n">
-        <v>-1205</v>
+        <v>-125</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
@@ -13991,15 +13065,15 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Biji Kapuk</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>3202</v>
+        <v>4168</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14011,14 +13085,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="H132" t="n">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
@@ -14028,52 +13102,52 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>5211</v>
+        <v>7515</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>625</v>
+        <v>451</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>-125</v>
+        <v>-451</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Biji Kapuk</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>4168</v>
+        <v>5148</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14085,14 +13159,14 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>500</v>
+        <v>283</v>
       </c>
       <c r="H134" t="n">
-        <v>500</v>
+        <v>283</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
@@ -14102,89 +13176,89 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>7515</v>
+        <v>8023</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>451</v>
+        <v>401</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="H135" t="n">
-        <v>-451</v>
+        <v>-289</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Sorgum</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>5148</v>
+        <v>4039</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>283</v>
+        <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>283</v>
+        <v>-202</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>8023</v>
+        <v>4006</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14192,147 +13266,83 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>401</v>
+        <v>200</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-289</v>
+        <v>-200</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>10</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>202</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>0</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4006</v>
+        <v>4933</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="H139" t="n">
-        <v>-200</v>
+        <v>217</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>12</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>326</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>391</v>
-      </c>
-      <c r="H140" t="n">
-        <v>65</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>4933</v>
+        <v>2830</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14344,14 +13354,14 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="H141" t="n">
-        <v>217</v>
+        <v>99</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
@@ -14361,89 +13371,89 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Tepung Bulu Ayam</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>3637</v>
+        <v>8038</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G142" t="n">
-        <v>156</v>
+        <v>273</v>
       </c>
       <c r="H142" t="n">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>2830</v>
+        <v>3582</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G143" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>99</v>
+        <v>-107</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Tepung Bulu Ayam</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>8038</v>
+        <v>8637</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -14455,14 +13465,14 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G144" t="n">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="H144" t="n">
-        <v>273</v>
+        <v>207</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
@@ -14472,180 +13482,106 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>3582</v>
+        <v>3332</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="H145" t="n">
-        <v>-107</v>
+        <v>70</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>8637</v>
+        <v>7908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="G146" t="n">
-        <v>207</v>
+        <v>71</v>
       </c>
       <c r="H146" t="n">
-        <v>207</v>
+        <v>-87</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
-        <v>19</v>
-      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>3332</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>5842</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G147" t="n">
-        <v>70</v>
+        <v>4472</v>
       </c>
       <c r="H147" t="n">
-        <v>70</v>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1370</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>20</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E148" t="n">
-        <v>158</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G148" t="n">
-        <v>71</v>
-      </c>
-      <c r="H148" t="n">
-        <v>-87</v>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E149" t="n">
-        <v>5842</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G149" t="n">
-        <v>4472</v>
-      </c>
-      <c r="H149" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="A148" t="inlineStr">
         <is>
           <t>Rp5,842/kg -&gt; Rp4,472/kg | HEMAT Rp1,370/kg (23.5%)</t>
         </is>
@@ -15124,47 +14060,6 @@
       <c r="A13" t="n">
         <v>8</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rum.Kecil</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Kambing Konservasi</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4324</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3079</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1245</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>28.8%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.02738957297862</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.667909466411548</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>OK optimal</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -15415,47 +14310,6 @@
       <c r="A20" t="n">
         <v>14</v>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Babi</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Babi Grower (25-60kg)</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>5863</v>
-      </c>
-      <c r="E20" t="n">
-        <v>3591</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2272</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>38.8%</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I20" t="n">
-        <v>15.10875174667749</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.959288535470492</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>OK optimal</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -15709,47 +14563,6 @@
     <row r="27">
       <c r="A27" t="n">
         <v>20</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Unggas</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Broiler Finisher (25-35d)</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>5903</v>
-      </c>
-      <c r="E27" t="n">
-        <v>4661</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1242</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>21.0%</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I27" t="n">
-        <v>18.06434663202504</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.211264356257215</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>OK optimal</t>
-        </is>
       </c>
     </row>
     <row r="28">

--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K121"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2452,38 +2452,6 @@
       <c r="A61" t="n">
         <v>5</v>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>12.5%</t>
-        </is>
-      </c>
-      <c r="G61" t="n">
-        <v>354</v>
-      </c>
-      <c r="H61" t="n">
-        <v>354</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2494,38 +2462,6 @@
       <c r="A63" t="n">
         <v>7</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>400</v>
-      </c>
-      <c r="H63" t="n">
-        <v>400</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3087,147 +3023,115 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>8</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Tepung Ikan</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>8023</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>401</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>0</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-401</v>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
-        <v>10</v>
-      </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>7908</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>158</v>
+        <v>6119</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>-158</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>6119</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0</v>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Sapi Hamil 7-9 Bulan</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Sapi Hamil 7-9 Bulan</t>
+      <c r="A87" t="n">
+        <v>1</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-1371</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4896</v>
+        <v>4039</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1371</v>
+        <v>727</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3238,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-1371</v>
+        <v>-727</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3248,23 +3152,23 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>727</v>
+        <v>320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3275,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-727</v>
+        <v>-320</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -3285,15 +3189,15 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3202</v>
+        <v>7984</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3301,7 +3205,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>320</v>
+        <v>798</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3312,7 +3216,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-320</v>
+        <v>-798</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -3322,15 +3226,15 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7984</v>
+        <v>4764</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3338,7 +3242,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>798</v>
+        <v>476</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3349,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-798</v>
+        <v>-476</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -3359,23 +3263,23 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pollard</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>4764</v>
+        <v>2386</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>476</v>
+        <v>119</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3386,7 +3290,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-476</v>
+        <v>-119</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -3396,15 +3300,15 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>2386</v>
+        <v>3637</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3412,7 +3316,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3423,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-119</v>
+        <v>-182</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -3433,23 +3337,23 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3637</v>
+        <v>4006</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3460,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-182</v>
+        <v>-100</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -3469,117 +3373,160 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
-        <v>9</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E95" t="n">
-        <v>100</v>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>10</v>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Sapi Laktasi Ringan</t>
+        </is>
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="n">
+        <v>1</v>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>4896</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5033</v>
+        <v>1567</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>211</v>
       </c>
       <c r="H97" t="n">
-        <v>0</v>
+        <v>-1356</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>UBAH</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+      <c r="A98" t="n">
+        <v>2</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Kulit Kentang</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2830</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>405</v>
+      </c>
+      <c r="H98" t="n">
+        <v>405</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sapi Laktasi Ringan</t>
+      <c r="A99" t="n">
+        <v>3</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Bungkil Kedelai</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>7984</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>14%</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1118</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-1118</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4896</v>
+        <v>4039</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1567</v>
+        <v>485</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>211</v>
+        <v>149</v>
       </c>
       <c r="H100" t="n">
-        <v>-1356</v>
+        <v>-336</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -3589,15 +3536,15 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2830</v>
+        <v>4933</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3609,14 +3556,14 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>405</v>
+        <v>562</v>
       </c>
       <c r="H101" t="n">
-        <v>405</v>
+        <v>562</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -3626,200 +3573,200 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>7984</v>
+        <v>3582</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="H102" t="n">
-        <v>-1118</v>
+        <v>383</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>4039</v>
+        <v>2386</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>485</v>
+        <v>0</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>149</v>
+        <v>222</v>
       </c>
       <c r="H103" t="n">
-        <v>-336</v>
+        <v>222</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4933</v>
+        <v>3202</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>562</v>
+        <v>192</v>
       </c>
       <c r="H104" t="n">
-        <v>562</v>
+        <v>-64</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>3582</v>
+        <v>8059</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>383</v>
+        <v>226</v>
       </c>
       <c r="H105" t="n">
-        <v>383</v>
+        <v>-419</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>2386</v>
+        <v>8637</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>222</v>
+        <v>-691</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>3202</v>
+        <v>4764</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3827,18 +3774,18 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="H107" t="n">
-        <v>-64</v>
+        <v>-357</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
@@ -3848,131 +3795,35 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>9</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Bungkil Kacang Tanah</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>645</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>226</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-419</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>10</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>691</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-691</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>11</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E110" t="n">
-        <v>381</v>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>24</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>8023</v>
+        <v>5211</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -3984,14 +3835,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>481</v>
+        <v>245</v>
       </c>
       <c r="H112" t="n">
-        <v>481</v>
+        <v>245</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
@@ -4001,20 +3852,52 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Dedak Halus</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>140</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>156</v>
+      </c>
+      <c r="H113" t="n">
+        <v>16</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>3332</v>
+        <v>8149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -4026,14 +3909,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="H114" t="n">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
@@ -4043,217 +3926,106 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>5211</v>
+        <v>7908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>245</v>
+        <v>-119</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>4006</v>
+        <v>5148</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="H116" t="n">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>18</v>
-      </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>8149</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>5583</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>171</v>
+        <v>4195</v>
       </c>
       <c r="H117" t="n">
-        <v>171</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1388</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
-        <v>19</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>119</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-119</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>20</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>5148</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>62</v>
-      </c>
-      <c r="H119" t="n">
-        <v>62</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>5583</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>4195</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
+      <c r="A118" t="inlineStr">
         <is>
           <t>Rp5,583/kg -&gt; Rp4,195/kg | HEMAT Rp1,388/kg (24.9%)</t>
         </is>
@@ -5795,38 +5567,6 @@
       <c r="A49" t="n">
         <v>2</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Bungkil Kedelai</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>7984</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1198</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-1198</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5837,38 +5577,6 @@
       <c r="A51" t="n">
         <v>4</v>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Gaplek</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>3202</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>256</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-256</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6251,38 +5959,6 @@
     <row r="65">
       <c r="A65" t="n">
         <v>10</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Biji Kapuk</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>4168</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>7.9%</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>329</v>
-      </c>
-      <c r="H65" t="n">
-        <v>329</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
       </c>
     </row>
     <row r="66">
@@ -9140,7 +8816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -10387,38 +10063,6 @@
       <c r="A42" t="n">
         <v>2</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Bungkil Kedelai</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>7984</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>18%</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>1437</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-1437</v>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -10429,38 +10073,6 @@
       <c r="A44" t="n">
         <v>4</v>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Gaplek</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>3202</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>13.0%</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>416</v>
-      </c>
-      <c r="H44" t="n">
-        <v>416</v>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -11177,38 +10789,6 @@
       <c r="A67" t="n">
         <v>6</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>143</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-143</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -11219,38 +10799,6 @@
       <c r="A69" t="n">
         <v>8</v>
       </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>244</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-244</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -11671,38 +11219,6 @@
       <c r="A84" t="n">
         <v>10</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>244</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>-244</v>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11710,64 +11226,75 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>5990</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>0</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0</v>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Rp5,990/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Rp5,990/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Layer Produksi</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Layer Produksi</t>
+      <c r="A88" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1616</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-1616</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>4896</v>
+        <v>7984</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1616</v>
+        <v>1277</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -11778,7 +11305,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-1616</v>
+        <v>-1277</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -11788,23 +11315,23 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7984</v>
+        <v>7908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1277</v>
+        <v>1186</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -11815,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-1277</v>
+        <v>-1186</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -11825,23 +11352,23 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Menir</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>7908</v>
+        <v>5211</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1186</v>
+        <v>521</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11852,7 +11379,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-1186</v>
+        <v>-521</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -11862,23 +11389,23 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Tepung Darah</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>5211</v>
+        <v>8149</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>521</v>
+        <v>244</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11889,7 +11416,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-521</v>
+        <v>-244</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -11899,15 +11426,15 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>8149</v>
+        <v>3582</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11915,7 +11442,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>244</v>
+        <v>107</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11926,7 +11453,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-244</v>
+        <v>-107</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -11936,15 +11463,15 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>3582</v>
+        <v>8023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11952,7 +11479,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>107</v>
+        <v>241</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11963,7 +11490,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>-107</v>
+        <v>-241</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -11973,23 +11500,23 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>8023</v>
+        <v>4006</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -12000,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>-241</v>
+        <v>-80</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -12009,98 +11536,130 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
-        <v>11</v>
-      </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>4006</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>80</v>
+        <v>6170</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>-80</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>6170</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0</v>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Rp6,170/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Rp6,170/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Bebek Petelur Starter</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Bebek Petelur Starter</t>
+      <c r="A99" t="n">
+        <v>6</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Mung Bean Husk</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>3332</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>423</v>
+      </c>
+      <c r="H99" t="n">
+        <v>423</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Menir</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>5211</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>625</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-625</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Biji Kapuk</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>2830</v>
+        <v>4168</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12112,14 +11671,14 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>634</v>
+        <v>358</v>
       </c>
       <c r="H101" t="n">
-        <v>634</v>
+        <v>358</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -12129,20 +11688,52 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4</v>
+        <v>9</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Tepung Darah</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>8149</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>326</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>7.4%</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>603</v>
+      </c>
+      <c r="H102" t="n">
+        <v>277</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>UBAH</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Tepung Bulu Ayam</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3202</v>
+        <v>8038</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12154,14 +11745,14 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="H103" t="n">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -12171,60 +11762,60 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mung Bean Husk</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>3332</v>
+        <v>4006</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>423</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>423</v>
+        <v>-240</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>5211</v>
+        <v>8023</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>625</v>
+        <v>481</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12235,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>-625</v>
+        <v>-481</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -12245,171 +11836,171 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Biji Kapuk</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>4168</v>
+        <v>7515</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>376</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G106" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>358</v>
+        <v>-376</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Tepung Darah</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>8149</v>
+        <v>4039</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>326</v>
+        <v>202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>603</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
-        <v>277</v>
+        <v>-202</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Tepung Bulu Ayam</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>8038</v>
+        <v>3582</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>506</v>
+        <v>54</v>
       </c>
       <c r="H108" t="n">
-        <v>506</v>
+        <v>-53</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>4006</v>
+        <v>7908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>240</v>
+        <v>158</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H109" t="n">
-        <v>-240</v>
+        <v>-79</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>8023</v>
+        <v>3637</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>481</v>
+        <v>73</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12420,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-481</v>
+        <v>-73</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -12429,172 +12020,101 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>13</v>
-      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>7515</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>376</v>
+        <v>5899</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>3739</v>
       </c>
       <c r="H111" t="n">
-        <v>-376</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>2160</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>14</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>202</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>15</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>107</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>54</v>
-      </c>
-      <c r="H113" t="n">
-        <v>-53</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>UBAH</t>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Bebek Petelur Layer</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Tepung Tulang</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>7908</v>
+        <v>4039</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>158</v>
+        <v>242</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>-79</v>
+        <v>-242</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>3637</v>
+        <v>3582</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12605,7 +12125,7 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>-73</v>
+        <v>-107</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
@@ -12614,318 +12134,389 @@
       </c>
     </row>
     <row r="116">
+      <c r="A116" t="n">
+        <v>10</v>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
+          <t>Bungkil Sawit</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>8201</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>246</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-246</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>11</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Tepung Ikan</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>8023</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>241</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-241</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="E116" t="n">
-        <v>5899</v>
-      </c>
-      <c r="F116" t="inlineStr">
+      <c r="E118" t="n">
+        <v>6053</v>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G116" t="n">
-        <v>3739</v>
-      </c>
-      <c r="H116" t="n">
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Bebek Petelur Layer</t>
-        </is>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
-        <v>5</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>242</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>0</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-242</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
-        <v>7</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>160</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-160</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Bebek Pedaging (Peking)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Jagung Pipilan</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3582</v>
+        <v>4896</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>107</v>
+        <v>1860</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>392</v>
       </c>
       <c r="H121" t="n">
-        <v>-107</v>
+        <v>-1468</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8201</v>
+        <v>2386</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="H122" t="n">
-        <v>-246</v>
+        <v>441</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>8023</v>
+        <v>7984</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>241</v>
+        <v>1437</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="H123" t="n">
-        <v>-241</v>
+        <v>-1205</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="n">
+        <v>4</v>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Gaplek</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3202</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6053</v>
+        <v>0</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>519</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>519</v>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+      <c r="A125" t="n">
+        <v>5</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Menir</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>5211</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>625</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>500</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Bebek Pedaging (Peking)</t>
+      <c r="A126" t="n">
+        <v>6</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Biji Kapuk</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4168</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>12.0%</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>500</v>
+      </c>
+      <c r="H126" t="n">
+        <v>500</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Corn Gluten Feed</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>4896</v>
+        <v>7515</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1860</v>
+        <v>451</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-1468</v>
+        <v>-451</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Sorgum</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>2386</v>
+        <v>5148</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12937,14 +12528,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>441</v>
+        <v>283</v>
       </c>
       <c r="H128" t="n">
-        <v>441</v>
+        <v>283</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -12954,34 +12545,34 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Tepung Ikan</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7984</v>
+        <v>8023</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1437</v>
+        <v>401</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>232</v>
+        <v>112</v>
       </c>
       <c r="H129" t="n">
-        <v>-1205</v>
+        <v>-289</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
@@ -12991,282 +12582,186 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>3202</v>
+        <v>4039</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>519</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>519</v>
+        <v>-202</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>5211</v>
+        <v>4006</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>625</v>
+        <v>200</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>-125</v>
+        <v>-200</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>6</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Biji Kapuk</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>4168</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
-        <v>0</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>500</v>
-      </c>
-      <c r="H132" t="n">
-        <v>500</v>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>7515</v>
+        <v>4933</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="H133" t="n">
-        <v>-451</v>
+        <v>217</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>8</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>5148</v>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>5.5%</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>283</v>
-      </c>
-      <c r="H134" t="n">
-        <v>283</v>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>8023</v>
+        <v>2830</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="H135" t="n">
-        <v>-289</v>
+        <v>99</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>10</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E136" t="n">
-        <v>202</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>4006</v>
+        <v>3582</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>200</v>
+        <v>107</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13277,7 +12772,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>-200</v>
+        <v>-107</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
@@ -13287,20 +12782,52 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Bungkil Kelapa</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>8637</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>207</v>
+      </c>
+      <c r="H138" t="n">
+        <v>207</v>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>4933</v>
+        <v>3332</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13312,14 +12839,14 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="H139" t="n">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
@@ -13329,259 +12856,69 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>14</v>
+        <v>20</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Tepung Tulang</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>7908</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>158</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>71</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-87</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>UBAH</t>
+        </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
-        <v>15</v>
-      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>2830</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>5842</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>99</v>
+        <v>4472</v>
       </c>
       <c r="H141" t="n">
-        <v>99</v>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1370</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
-        <v>16</v>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Tepung Bulu Ayam</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>8038</v>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E142" t="n">
-        <v>0</v>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>3.4%</t>
-        </is>
-      </c>
-      <c r="G142" t="n">
-        <v>273</v>
-      </c>
-      <c r="H142" t="n">
-        <v>273</v>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>17</v>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E143" t="n">
-        <v>107</v>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G143" t="n">
-        <v>0</v>
-      </c>
-      <c r="H143" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>18</v>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E144" t="n">
-        <v>0</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="G144" t="n">
-        <v>207</v>
-      </c>
-      <c r="H144" t="n">
-        <v>207</v>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>19</v>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E145" t="n">
-        <v>0</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="G145" t="n">
-        <v>70</v>
-      </c>
-      <c r="H145" t="n">
-        <v>70</v>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>20</v>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E146" t="n">
-        <v>158</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G146" t="n">
-        <v>71</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-87</v>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E147" t="n">
-        <v>5842</v>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G147" t="n">
-        <v>4472</v>
-      </c>
-      <c r="H147" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
+      <c r="A142" t="inlineStr">
         <is>
           <t>Rp5,842/kg -&gt; Rp4,472/kg | HEMAT Rp1,370/kg (23.5%)</t>
         </is>

--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3037,64 +3037,75 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>6119</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0</v>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Rp6,119/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Sapi Hamil 7-9 Bulan</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sapi Hamil 7-9 Bulan</t>
+      <c r="A86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Jagung Pipilan</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>4896</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>28%</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1371</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-1371</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>4896</v>
+        <v>4039</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1371</v>
+        <v>727</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -3105,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>-1371</v>
+        <v>-727</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -3115,23 +3126,23 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>727</v>
+        <v>320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -3142,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>-727</v>
+        <v>-320</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -3152,15 +3163,15 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Bungkil Kedelai</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>3202</v>
+        <v>7984</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3168,7 +3179,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>320</v>
+        <v>798</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -3179,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>-320</v>
+        <v>-798</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
@@ -3189,15 +3200,15 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>7984</v>
+        <v>4764</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3205,7 +3216,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>798</v>
+        <v>476</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -3216,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>-798</v>
+        <v>-476</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -3226,23 +3237,23 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pollard</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4764</v>
+        <v>2386</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>476</v>
+        <v>119</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3253,7 +3264,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>-476</v>
+        <v>-119</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
@@ -3263,15 +3274,15 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>2386</v>
+        <v>3637</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3279,7 +3290,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -3290,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>-119</v>
+        <v>-182</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
@@ -3300,23 +3311,23 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3637</v>
+        <v>4006</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>182</v>
+        <v>100</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -3327,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>-182</v>
+        <v>-100</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -3336,197 +3347,165 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
-        <v>9</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2.5%</t>
-        </is>
-      </c>
-      <c r="E94" t="n">
-        <v>100</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G94" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Rp5,033/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
+          <t>Sapi Laktasi Ringan</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sapi Laktasi Ringan</t>
+      <c r="A96" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Kulit Kentang</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2830</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>405</v>
+      </c>
+      <c r="H96" t="n">
+        <v>405</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1</v>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Jagung Pipilan</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>4896</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>32%</t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>1567</v>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
-      <c r="G97" t="n">
-        <v>211</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-1356</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>3</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>2830</v>
+        <v>4039</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>485</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>405</v>
+        <v>149</v>
       </c>
       <c r="H98" t="n">
-        <v>405</v>
+        <v>-336</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>7984</v>
+        <v>2386</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1118</v>
+        <v>0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>222</v>
       </c>
       <c r="H99" t="n">
-        <v>-1118</v>
+        <v>222</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Gaplek</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>4039</v>
+        <v>3202</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>485</v>
+        <v>256</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="H100" t="n">
-        <v>-336</v>
+        <v>-64</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -3536,496 +3515,194 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Bungkil Kacang Tanah</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>4933</v>
+        <v>8059</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>2.8%</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>562</v>
+        <v>226</v>
       </c>
       <c r="H101" t="n">
-        <v>562</v>
+        <v>-419</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>3582</v>
+        <v>8637</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G102" t="n">
-        <v>383</v>
+        <v>0</v>
       </c>
       <c r="H102" t="n">
-        <v>383</v>
+        <v>-691</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>2386</v>
+        <v>4764</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>381</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>222</v>
+        <v>24</v>
       </c>
       <c r="H103" t="n">
-        <v>222</v>
+        <v>-357</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>8</v>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Gaplek</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>3202</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E104" t="n">
-        <v>256</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>6.0%</t>
-        </is>
-      </c>
-      <c r="G104" t="n">
-        <v>192</v>
-      </c>
-      <c r="H104" t="n">
-        <v>-64</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>9</v>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Bungkil Kacang Tanah</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>645</v>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G105" t="n">
-        <v>226</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-419</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>10</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>691</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-691</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>11</v>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
-        <v>381</v>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G107" t="n">
-        <v>24</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Dedak Halus</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>140</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>156</v>
+      </c>
+      <c r="H109" t="n">
+        <v>16</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>16</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Menir</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>5211</v>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
-        <v>0</v>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>4.7%</t>
-        </is>
-      </c>
-      <c r="G112" t="n">
-        <v>245</v>
-      </c>
-      <c r="H112" t="n">
-        <v>245</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>17</v>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
-        <v>140</v>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="G113" t="n">
-        <v>156</v>
-      </c>
-      <c r="H113" t="n">
-        <v>16</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>18</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>171</v>
-      </c>
-      <c r="H114" t="n">
-        <v>171</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>19</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>119</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-119</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>20</v>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>5148</v>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" t="n">
-        <v>0</v>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>1.2%</t>
-        </is>
-      </c>
-      <c r="G116" t="n">
-        <v>62</v>
-      </c>
-      <c r="H116" t="n">
-        <v>62</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>5583</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>4195</v>
-      </c>
-      <c r="H117" t="n">
-        <v>1388</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A113" t="inlineStr">
         <is>
           <t>Rp5,583/kg -&gt; Rp4,195/kg | HEMAT Rp1,388/kg (24.9%)</t>
         </is>
@@ -8816,7 +8493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K142"/>
+  <dimension ref="A1:K132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11651,208 +11328,144 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>8</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Biji Kapuk</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>4168</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>8.6%</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>358</v>
-      </c>
-      <c r="H101" t="n">
-        <v>358</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>9</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Tepung Darah</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>8149</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>326</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>603</v>
-      </c>
-      <c r="H102" t="n">
-        <v>277</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tepung Bulu Ayam</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8038</v>
+        <v>4039</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0</v>
+        <v>202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G103" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>506</v>
+        <v>-202</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>4006</v>
+        <v>3582</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>240</v>
+        <v>107</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="H104" t="n">
-        <v>-240</v>
+        <v>-53</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Tepung Tulang</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>8023</v>
+        <v>7908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>481</v>
+        <v>158</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="H105" t="n">
-        <v>-481</v>
+        <v>-79</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Molases</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>7515</v>
+        <v>3637</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>376</v>
+        <v>73</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11863,7 +11476,7 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>-376</v>
+        <v>-73</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
@@ -11872,135 +11485,64 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
-        <v>14</v>
-      </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>4039</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>202</v>
+        <v>5899</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>3739</v>
       </c>
       <c r="H107" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>2160</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
-        <v>15</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E108" t="n">
-        <v>107</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>1.5%</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>54</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-53</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>UBAH</t>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>16</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>158</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>1.0%</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>79</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-79</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>UBAH</t>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Bebek Petelur Layer</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Molases</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3637</v>
+        <v>4039</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>6%</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12011,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>-73</v>
+        <v>-242</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
@@ -12020,474 +11562,492 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="n">
+        <v>9</v>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>TOTAL</t>
-        </is>
+          <t>Ampas Tahu</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3582</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5899</v>
+        <v>107</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>3739</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>2160</v>
+        <v>-107</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Rp5,899/kg -&gt; Rp3,739/kg | HEMAT Rp2,160/kg (36.6%)</t>
+      <c r="A112" t="n">
+        <v>10</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Bungkil Sawit</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>8201</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>246</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-246</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Bebek Petelur Layer</t>
+      <c r="A113" t="n">
+        <v>11</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tepung Ikan</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>8023</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>241</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-241</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v>5</v>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>6%</t>
-        </is>
-      </c>
-      <c r="E114" t="n">
-        <v>242</v>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-242</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
-        <v>9</v>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E115" t="n">
-        <v>107</v>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="n">
-        <v>0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Bebek Pedaging (Peking)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Bungkil Sawit</t>
+          <t>Onggok</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>8201</v>
+        <v>2386</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="H116" t="n">
-        <v>-246</v>
+        <v>441</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>Menir</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>5211</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>625</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>9.6%</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>500</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-125</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>UBAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>7</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Corn Gluten Feed</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>7515</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>6%</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>451</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-451</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>8</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Sorgum</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>5148</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>0</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>283</v>
+      </c>
+      <c r="H119" t="n">
+        <v>283</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>BARU</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>Tepung Ikan</t>
         </is>
       </c>
-      <c r="C117" t="n">
+      <c r="C120" t="n">
         <v>8023</v>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
-        <v>241</v>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" t="n">
-        <v>0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-241</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>6053</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>0</v>
-      </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Rp6,053/kg -&gt; Rp0/kg | HEMAT Rp0/kg (0.0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Bebek Pedaging (Peking)</t>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>401</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1.4%</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>112</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-289</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Jagung Pipilan</t>
+          <t>Dedak Padi</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4896</v>
+        <v>4039</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1860</v>
+        <v>202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>392</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-1468</v>
+        <v>-202</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Dedak Halus</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>2386</v>
+        <v>4006</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>441</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>441</v>
+        <v>-200</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Bungkil Kedelai</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>7984</v>
+        <v>4933</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1437</v>
+        <v>0</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="H123" t="n">
-        <v>-1205</v>
+        <v>217</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4</v>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Gaplek</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>3202</v>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" t="n">
-        <v>0</v>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>16.2%</t>
-        </is>
-      </c>
-      <c r="G124" t="n">
-        <v>519</v>
-      </c>
-      <c r="H124" t="n">
-        <v>519</v>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Menir</t>
+          <t>Kulit Kentang</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>5211</v>
+        <v>2830</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>500</v>
+        <v>99</v>
       </c>
       <c r="H125" t="n">
-        <v>-125</v>
+        <v>99</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>6</v>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Biji Kapuk</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>4168</v>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" t="n">
-        <v>0</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>12.0%</t>
-        </is>
-      </c>
-      <c r="G126" t="n">
-        <v>500</v>
-      </c>
-      <c r="H126" t="n">
-        <v>500</v>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>7515</v>
+        <v>3582</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>451</v>
+        <v>107</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12498,7 +12058,7 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>-451</v>
+        <v>-107</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
@@ -12508,15 +12068,15 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Sorgum</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>5148</v>
+        <v>8637</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12528,14 +12088,14 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="H128" t="n">
-        <v>283</v>
+        <v>207</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
@@ -12545,380 +12105,74 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Tepung Ikan</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>8023</v>
+        <v>3332</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>401</v>
+        <v>0</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H129" t="n">
-        <v>-289</v>
+        <v>70</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>UBAH</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>10</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E130" t="n">
-        <v>202</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
-        <v>11</v>
-      </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>4006</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>200</v>
+        <v>5842</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>4472</v>
       </c>
       <c r="H131" t="n">
-        <v>-200</v>
-      </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>1370</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>13</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Rice Polish</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>4933</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E133" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>217</v>
-      </c>
-      <c r="H133" t="n">
-        <v>217</v>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>15</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>2830</v>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>0</v>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>99</v>
-      </c>
-      <c r="H135" t="n">
-        <v>99</v>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>17</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E137" t="n">
-        <v>107</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>18</v>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E138" t="n">
-        <v>0</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="G138" t="n">
-        <v>207</v>
-      </c>
-      <c r="H138" t="n">
-        <v>207</v>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>19</v>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E139" t="n">
-        <v>0</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="G139" t="n">
-        <v>70</v>
-      </c>
-      <c r="H139" t="n">
-        <v>70</v>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>20</v>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Tepung Tulang</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>7908</v>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2%</t>
-        </is>
-      </c>
-      <c r="E140" t="n">
-        <v>158</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>0.9%</t>
-        </is>
-      </c>
-      <c r="G140" t="n">
-        <v>71</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-87</v>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E141" t="n">
-        <v>5842</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G141" t="n">
-        <v>4472</v>
-      </c>
-      <c r="H141" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="A132" t="inlineStr">
         <is>
           <t>Rp5,842/kg -&gt; Rp4,472/kg | HEMAT Rp1,370/kg (23.5%)</t>
         </is>

--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3441,52 +3441,52 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Onggok</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>2386</v>
+        <v>8637</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>691</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>222</v>
+        <v>-691</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>BARU</t>
+          <t>HAPUS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Gaplek</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>3202</v>
+        <v>4764</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3494,18 +3494,18 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>256</v>
+        <v>381</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="H100" t="n">
-        <v>-64</v>
+        <v>-357</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -3515,194 +3515,83 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>9</v>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Bungkil Kacang Tanah</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>8059</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>645</v>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2.8%</t>
-        </is>
-      </c>
-      <c r="G101" t="n">
-        <v>226</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-419</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>10</v>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E102" t="n">
-        <v>691</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-691</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>11</v>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>381</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>24</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>14</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Dedak Halus</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>140</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>156</v>
+      </c>
+      <c r="H106" t="n">
+        <v>16</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>17</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E109" t="n">
-        <v>140</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>156</v>
-      </c>
-      <c r="H109" t="n">
-        <v>16</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+      <c r="A110" t="inlineStr">
         <is>
           <t>Rp5,583/kg -&gt; Rp4,195/kg | HEMAT Rp1,388/kg (24.9%)</t>
         </is>
@@ -8493,7 +8382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11340,38 +11229,6 @@
       <c r="A103" t="n">
         <v>14</v>
       </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Dedak Padi</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>4039</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E103" t="n">
-        <v>202</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G103" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-202</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11762,134 +11619,70 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Corn Gluten Feed</t>
+          <t>Rice Polish</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>7515</v>
+        <v>4933</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>6%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>217</v>
       </c>
       <c r="H118" t="n">
-        <v>-451</v>
+        <v>217</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>8</v>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Sorgum</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>5148</v>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" t="n">
-        <v>0</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>5.5%</t>
-        </is>
-      </c>
-      <c r="G119" t="n">
-        <v>283</v>
-      </c>
-      <c r="H119" t="n">
-        <v>283</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>15</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>9</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Tepung Ikan</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>8023</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>401</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>1.4%</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>112</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-289</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>16</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Dedak Padi</t>
+          <t>Ampas Tahu</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>4039</v>
+        <v>3582</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>202</v>
+        <v>107</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11900,7 +11693,7 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>-202</v>
+        <v>-107</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -11910,52 +11703,52 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dedak Halus</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>4006</v>
+        <v>8637</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="H122" t="n">
-        <v>-200</v>
+        <v>207</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Rice Polish</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>4933</v>
+        <v>3332</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11967,14 +11760,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="H123" t="n">
-        <v>217</v>
+        <v>70</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -11984,195 +11777,37 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>15</v>
-      </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Kulit Kentang</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>2830</v>
+          <t>TOTAL</t>
+        </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0</v>
+        <v>5842</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>99</v>
+        <v>4472</v>
       </c>
       <c r="H125" t="n">
-        <v>99</v>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>1370</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
-        <v>17</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
-        <v>107</v>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
-        <v>18</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Bungkil Kelapa</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>8637</v>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>207</v>
-      </c>
-      <c r="H128" t="n">
-        <v>207</v>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>19</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E129" t="n">
-        <v>0</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>70</v>
-      </c>
-      <c r="H129" t="n">
-        <v>70</v>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E131" t="n">
-        <v>5842</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>4472</v>
-      </c>
-      <c r="H131" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="A126" t="inlineStr">
         <is>
           <t>Rp5,842/kg -&gt; Rp4,472/kg | HEMAT Rp1,370/kg (23.5%)</t>
         </is>

--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -637,7 +637,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3441,15 +3441,15 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Pollard</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>8637</v>
+        <v>4764</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3457,141 +3457,104 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>691</v>
+        <v>381</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="H99" t="n">
-        <v>-691</v>
+        <v>-357</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>UBAH</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>11</v>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E100" t="n">
-        <v>381</v>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G100" t="n">
-        <v>24</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
+        <v>17</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dedak Halus</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>4006</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>140</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>156</v>
+      </c>
+      <c r="H105" t="n">
         <v>16</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>17</v>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Dedak Halus</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>4006</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="E106" t="n">
-        <v>140</v>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="G106" t="n">
-        <v>156</v>
-      </c>
-      <c r="H106" t="n">
-        <v>16</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
+        <v>18</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
+      <c r="A109" t="inlineStr">
         <is>
           <t>Rp5,583/kg -&gt; Rp4,195/kg | HEMAT Rp1,388/kg (24.9%)</t>
         </is>
@@ -8382,7 +8345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -11619,99 +11582,99 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>13</v>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Rice Polish</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>4933</v>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
-        <v>0</v>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="G118" t="n">
-        <v>217</v>
-      </c>
-      <c r="H118" t="n">
-        <v>217</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>15</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ampas Tahu</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>3582</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>107</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-107</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>HAPUS</t>
+        </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Ampas Tahu</t>
+          <t>Bungkil Kelapa</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>3582</v>
+        <v>8637</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
       <c r="H121" t="n">
-        <v>-107</v>
+        <v>207</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>HAPUS</t>
+          <t>BARU</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bungkil Kelapa</t>
+          <t>Mung Bean Husk</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8637</v>
+        <v>3332</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11723,14 +11686,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.1%</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="H122" t="n">
-        <v>207</v>
+        <v>70</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -11740,74 +11703,37 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>19</v>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Mung Bean Husk</t>
-        </is>
-      </c>
-      <c r="C123" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
-        <v>0</v>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2.1%</t>
-        </is>
-      </c>
-      <c r="G123" t="n">
-        <v>70</v>
-      </c>
-      <c r="H123" t="n">
-        <v>70</v>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>BARU</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>20</v>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>5842</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>4472</v>
+      </c>
+      <c r="H124" t="n">
+        <v>1370</v>
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E125" t="n">
-        <v>5842</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G125" t="n">
-        <v>4472</v>
-      </c>
-      <c r="H125" t="n">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
+      <c r="A125" t="inlineStr">
         <is>
           <t>Rp5,842/kg -&gt; Rp4,472/kg | HEMAT Rp1,370/kg (23.5%)</t>
         </is>

--- a/data/optimalisasi_pakan.xlsx
+++ b/data/optimalisasi_pakan.xlsx
@@ -3443,38 +3443,6 @@
       <c r="A99" t="n">
         <v>11</v>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Pollard</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>4764</v>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="E99" t="n">
-        <v>381</v>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="G99" t="n">
-        <v>24</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-357</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>UBAH</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11593,38 +11561,6 @@
     <row r="120">
       <c r="A120" t="n">
         <v>17</v>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Ampas Tahu</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>3582</v>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
-      </c>
-      <c r="E120" t="n">
-        <v>107</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-107</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>HAPUS</t>
-        </is>
       </c>
     </row>
     <row r="121">
